--- a/data/trans_camb/P1416-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1416-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,26</t>
+          <t>-3,3; 0,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; -1,25</t>
+          <t>-4,49; -1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,15</t>
+          <t>-1,91; 2,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -0,57</t>
+          <t>-4,27; -0,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; -0,55</t>
+          <t>-4,45; -0,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 4,47</t>
+          <t>0,78; 4,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; -0,66</t>
+          <t>-3,56; -0,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -1,36</t>
+          <t>-3,99; -1,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 3,17</t>
+          <t>0,29; 3,45</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 8,09</t>
+          <t>-55,32; 14,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-75,07; -27,08</t>
+          <t>-75,37; -26,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 72,32</t>
+          <t>-32,0; 64,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,52; -8,55</t>
+          <t>-51,06; -10,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,3; -8,94</t>
+          <t>-53,71; -6,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 69,45</t>
+          <t>8,85; 75,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,06; -11,48</t>
+          <t>-49,65; -14,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,24; -22,46</t>
+          <t>-56,53; -20,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 55,22</t>
+          <t>4,1; 58,35</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>2,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 0,21</t>
+          <t>-3,09; 0,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; -0,28</t>
+          <t>-3,54; -0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 6,0</t>
+          <t>2,15; 6,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,01</t>
+          <t>-4,45; -0,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -0,09</t>
+          <t>-4,15; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,81</t>
+          <t>-0,82; 3,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,52</t>
+          <t>-3,02; -0,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,62</t>
+          <t>-3,26; -0,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,26</t>
+          <t>1,24; 4,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,53%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 3,64</t>
+          <t>-39,59; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,1; -4,39</t>
+          <t>-45,64; -4,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 96,09</t>
+          <t>26,98; 107,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,55; -0,3</t>
+          <t>-37,2; -2,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,34; -0,85</t>
+          <t>-34,79; -1,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 18,15</t>
+          <t>-7,39; 30,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -6,7</t>
+          <t>-32,2; -6,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,95; -7,4</t>
+          <t>-34,06; -9,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 39,46</t>
+          <t>13,0; 50,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,52</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 1,3</t>
+          <t>-5,59; 1,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 3,29</t>
+          <t>-3,96; 3,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 2,34</t>
+          <t>-3,72; 3,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,95</t>
+          <t>-6,37; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,09</t>
+          <t>-5,06; 3,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,51</t>
+          <t>-0,85; 6,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 0,92</t>
+          <t>-4,61; 0,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,08</t>
+          <t>-3,16; 2,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,54</t>
+          <t>-1,21; 3,85</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-8,98%</t>
+          <t>-5,79%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-53,78; 21,89</t>
+          <t>-52,75; 16,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,03; 45,45</t>
+          <t>-36,71; 44,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 34,34</t>
+          <t>-34,43; 47,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,3; 29,59</t>
+          <t>-44,86; 20,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 31,54</t>
+          <t>-36,06; 33,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 69,61</t>
+          <t>-6,18; 74,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,8; 10,34</t>
+          <t>-40,99; 9,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 23,91</t>
+          <t>-27,61; 27,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 40,06</t>
+          <t>-10,3; 43,58</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>2,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,46</t>
+          <t>-2,73; -0,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; -0,68</t>
+          <t>-2,82; -0,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,43</t>
+          <t>1,42; 4,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,96</t>
+          <t>-3,7; -0,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,28</t>
+          <t>-2,93; -0,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,57</t>
+          <t>1,05; 3,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; -0,93</t>
+          <t>-2,72; -1,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,76</t>
+          <t>-2,51; -0,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,23</t>
+          <t>1,72; 3,79</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,51; -6,61</t>
+          <t>-37,52; -6,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,35; -10,67</t>
+          <t>-39,25; -10,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,29; 71,01</t>
+          <t>19,4; 70,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,53; -11,15</t>
+          <t>-34,88; -10,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,66; -3,2</t>
+          <t>-28,38; -3,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 28,52</t>
+          <t>9,89; 43,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,49; -12,2</t>
+          <t>-32,0; -13,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,83; -10,08</t>
+          <t>-29,2; -9,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 41,37</t>
+          <t>20,06; 49,06</t>
         </is>
       </c>
     </row>
